--- a/spring-boot-starter-module/spring-boot-starter-components/spring-boot-starter-excel/exportTemplate.xlsx
+++ b/spring-boot-starter-module/spring-boot-starter-components/spring-boot-starter-excel/exportTemplate.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>JIM</author>
+    <author>windows</author>
   </authors>
   <commentList>
     <comment ref="A5" authorId="0">
@@ -42,7 +42,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>/data/records</t>
+          <t>${/data/records}</t>
         </r>
       </text>
     </comment>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>客户数据</t>
   </si>
@@ -59,16 +59,13 @@
     <t>当前页:</t>
   </si>
   <si>
-    <t>{=/data/current}</t>
+    <t>${/data/current}</t>
   </si>
   <si>
     <t>总页数:</t>
   </si>
   <si>
-    <t>{=/data/pages}</t>
-  </si>
-  <si>
-    <t>序号</t>
+    <t>${/data/pages}</t>
   </si>
   <si>
     <t>编号</t>
@@ -86,34 +83,31 @@
     <t>-</t>
   </si>
   <si>
-    <t>{=/index}</t>
-  </si>
-  <si>
-    <t>{=/cusCode}</t>
-  </si>
-  <si>
-    <t>{=/cusName}</t>
-  </si>
-  <si>
-    <t>{=/cusIdCardNum}</t>
-  </si>
-  <si>
-    <t>{=/cusPhone}</t>
+    <t>${/cusCode}</t>
+  </si>
+  <si>
+    <t>${/cusName}</t>
+  </si>
+  <si>
+    <t>${/cusIdCardNum}</t>
+  </si>
+  <si>
+    <t>${/cusPhone}</t>
   </si>
   <si>
     <t>总人数</t>
   </si>
   <si>
-    <t>{=/data.total}</t>
-  </si>
-  <si>
-    <t>备注：{=/remark}</t>
+    <t>${data.total}</t>
+  </si>
+  <si>
+    <t>备注：${/remark}</t>
   </si>
   <si>
     <t>时间戳</t>
   </si>
   <si>
-    <t>{=/timestamp}</t>
+    <t>${/timestamp}</t>
   </si>
 </sst>
 </file>
@@ -512,7 +506,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -521,43 +515,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -830,7 +794,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -842,34 +806,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -954,7 +918,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -981,46 +945,40 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1390,7 +1348,7 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="26.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.925" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="25.375" style="3" customWidth="1"/>
     <col min="4" max="4" width="20.3333333333333" style="3" customWidth="1"/>
@@ -1448,87 +1406,87 @@
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>10</v>
+      <c r="F4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:9">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>10</v>
+      <c r="E5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="1:9">
-      <c r="A6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="20"/>
+      <c r="A6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="1:9">
-      <c r="A7" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="23"/>
+      <c r="A7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:9">
       <c r="A8" s="6"/>
@@ -1542,39 +1500,39 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>20</v>
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="24"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
     </row>
     <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="24"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/spring-boot-starter-module/spring-boot-starter-components/spring-boot-starter-excel/exportTemplate.xlsx
+++ b/spring-boot-starter-module/spring-boot-starter-components/spring-boot-starter-excel/exportTemplate.xlsx
@@ -53,7 +53,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
-    <t>客户数据</t>
+    <t>客户数据导出模板</t>
   </si>
   <si>
     <t>当前页:</t>
